--- a/blog.xlsx
+++ b/blog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sefazpegovbr-my.sharepoint.com/personal/filipe_lima_sefaz_pe_gov_br/Documents/Documents/GitHub/Fantasy-unificado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="338" documentId="8_{B9426EDD-9454-4E3A-A069-F78DEAA6A3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EC6BA20-8D06-40FD-AADF-E2C15E90AB74}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="8_{B9426EDD-9454-4E3A-A069-F78DEAA6A3A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5D490F3-2534-4E02-99B9-7EAB7DE13654}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AAEAB4D0-440E-4EC9-A9CD-FD3BB0FD2CA8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{AAEAB4D0-440E-4EC9-A9CD-FD3BB0FD2CA8}"/>
   </bookViews>
   <sheets>
     <sheet name="config_tabs" sheetId="1" r:id="rId1"/>
@@ -1147,6 +1147,7 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
   </cols>
